--- a/templates/generic_transactions_template.xlsx
+++ b/templates/generic_transactions_template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$K$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -506,17 +506,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,35 +530,50 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ex Date</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Coverage Start</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Coverage End</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Price Per Share</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Fees</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -565,19 +583,26 @@
       <c r="A2" s="3" t="n">
         <v>46036</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>DEPOSIT</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n">
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Transfer from checking</t>
         </is>
@@ -587,27 +612,34 @@
       <c r="A3" s="3" t="n">
         <v>46037</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>27.5</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Initial purchase</t>
         </is>
@@ -617,23 +649,32 @@
       <c r="A4" s="3" t="n">
         <v>46056</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>46052</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n">
         <v>8.25</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Cash dividend received</t>
         </is>
@@ -643,27 +684,34 @@
       <c r="A5" s="3" t="n">
         <v>46056</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>DRIP</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>27.5</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Dividend reinvestment shares</t>
         </is>
@@ -673,23 +721,30 @@
       <c r="A6" s="3" t="n">
         <v>46073</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>TRANSFER IN</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>JEPI</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Shares moved from another broker</t>
         </is>
@@ -699,27 +754,34 @@
       <c r="A7" s="3" t="n">
         <v>46091</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="H7" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Partial sale</t>
         </is>
@@ -729,28 +791,35 @@
       <c r="A8" s="3" t="n">
         <v>46093</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>WITHDRAWAL</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n">
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Transfer to checking</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:K8"/>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid transaction type" error="Choose BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST." promptTitle="Transaction type" prompt="Select the kind of transaction." type="list">
+    <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid transaction type" error="Choose BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST." promptTitle="Transaction type" prompt="Select the kind of transaction." type="list">
       <formula1>"BUY,SELL,DIVIDEND,DRIP,DEPOSIT,WITHDRAWAL,TRANSFER IN,TRANSFER OUT,FEE,INTEREST"</formula1>
     </dataValidation>
   </dataValidations>
@@ -764,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -834,166 +903,232 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Ex Date</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dividends (recommended)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Determines how the row affects holdings, income, and account cash flows.</t>
+          <t>Ex-dividend date used for investment-performance timing; cash totals still use Date.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST</t>
+          <t>2026-01-30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Ticker</t>
+          <t>Coverage Start</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Securities only</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Security ticker, trimmed and uppercased. Leave blank for DEPOSIT, WITHDRAWAL, FEE, and INTEREST.</t>
+          <t>First date for which this file contains complete broker activity and distributions.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>2026-01-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Shares</t>
+          <t>Coverage End</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Trades and transfers</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Positive share quantity for BUY, SELL, DRIP, TRANSFER IN, and TRANSFER OUT.</t>
+          <t>Last date for which this file contains complete broker activity and distributions.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>10 or 0.3250</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Price Per Share</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Trades only</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Execution price for BUY, SELL, and DRIP. Optional for transfers; blank values them at that day's close.</t>
+          <t>Determines how the row affects holdings, income, and account cash flows.</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>27.50</t>
+          <t>BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Ticker</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Securities only</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Commission or transaction fee; blank defaults to zero.</t>
+          <t>Security ticker, trimmed and uppercased. Leave blank for DEPOSIT, WITHDRAWAL, FEE, and INTEREST.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>SCHD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Shares</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Cash rows</t>
+          <t>Trades and transfers</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Total cash for DIVIDEND, DEPOSIT, WITHDRAWAL, FEE, and INTEREST rows. Enter it as a positive number; the type decides whether money came in or went out (INTEREST keeps its sign, so margin interest charged can be negative).</t>
+          <t>Positive share quantity for BUY, SELL, DRIP, TRANSFER IN, and TRANSFER OUT.</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>8.25 or 5000</t>
+          <t>10 or 0.3250</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>Price Per Share</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Trades only</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Execution price for BUY, SELL, and DRIP. Optional for transfers; blank values them at that day's close.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>27.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Commission or transaction fee; blank defaults to zero.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Cash rows</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Total cash for DIVIDEND, DEPOSIT, WITHDRAWAL, FEE, and INTEREST rows. Enter it as a positive number; the type decides whether money came in or went out (INTEREST keeps its sign, so margin interest charged can be negative).</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>8.25 or 5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Optional description saved with the transaction.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Initial purchase</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>BUY, SELL, and DRIP rows update positions when the transaction ledger is the portfolio's source of truth. If current holdings already exist, the import keeps those share counts and adds the transactions for history, cost-basis support, dividend tracking, and realized gains—matching broker transaction imports.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="72" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="20" ht="72" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Account Alpha on the Dashboard: DEPOSIT, WITHDRAWAL, TRANSFER IN, and TRANSFER OUT rows let the app separate money you added or took out from what the account earned. When a file contains any of these rows, the app treats the file's first-to-last date as a complete record of money in and out, so include every deposit and withdrawal for that stretch. A period with no money movements can be marked complete on the Holdings screen under Deposits &amp; Withdrawals.</t>
         </is>
@@ -1002,9 +1137,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/generic_transactions_template.xlsx
+++ b/templates/generic_transactions_template.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Transactions'!$A$1:$L$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,9 +108,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -124,6 +125,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="1" min="1" max="1"/>
@@ -519,308 +523,321 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" style="2" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Ex Date</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Coverage Start</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Coverage End</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Price Per Share</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Fees</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Split Ratio</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>DEPOSIT</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="5" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="7" t="n">
         <v>5000</v>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Transfer from checking</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>46037</v>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="6" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="J3" s="7" t="n"/>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Initial purchase</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>46056</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>46052</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>DIVIDEND</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n">
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n">
         <v>8.25</v>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Cash dividend received</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>46056</v>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>DRIP</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>27.5</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Dividend reinvestment shares</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>46073</v>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>TRANSFER IN</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>JEPI</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Shares moved from another broker</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>46091</v>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.05</v>
       </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Partial sale</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n">
         <v>46036</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>46093</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>WITHDRAWAL</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n">
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Transfer to checking</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K8"/>
+  <autoFilter ref="A1:L8"/>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid transaction type" error="Choose BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST." promptTitle="Transaction type" prompt="Select the kind of transaction." type="list">
-      <formula1>"BUY,SELL,DIVIDEND,DRIP,DEPOSIT,WITHDRAWAL,TRANSFER IN,TRANSFER OUT,FEE,INTEREST"</formula1>
+    <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid transaction type" error="Choose BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, INTEREST, SPLIT, or REVERSE SPLIT." promptTitle="Transaction type" prompt="Select the kind of transaction." type="list">
+      <formula1>"BUY,SELL,DIVIDEND,DRIP,DEPOSIT,WITHDRAWAL,TRANSFER IN,TRANSFER OUT,FEE,INTEREST,SPLIT,REVERSE SPLIT"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -833,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -843,292 +860,314 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Generic Transactions Import Template</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Import one portfolio at a time. Select the destination portfolio in the app, preview the file, then import it.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>How it is used</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Accepted values / example</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Transaction, trade, or payment date.</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>2026-01-15 or 01/15/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Ex Date</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Dividends (recommended)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Ex-dividend date used for investment-performance timing; cash totals still use Date.</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>2026-01-30</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Coverage Start</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>First date for which this file contains complete broker activity and distributions.</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Coverage End</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Last date for which this file contains complete broker activity and distributions.</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Determines how the row affects holdings, income, and account cash flows.</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, or INTEREST</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>BUY, SELL, DIVIDEND, DRIP, DEPOSIT, WITHDRAWAL, TRANSFER IN, TRANSFER OUT, FEE, INTEREST, SPLIT, or REVERSE SPLIT</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Securities only</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Security ticker, trimmed and uppercased. Leave blank for DEPOSIT, WITHDRAWAL, FEE, and INTEREST.</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>SCHD</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Trades and transfers</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Positive share quantity for BUY, SELL, DRIP, TRANSFER IN, and TRANSFER OUT.</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>10 or 0.3250</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Price Per Share</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Trades only</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Execution price for BUY, SELL, and DRIP. Optional for transfers; blank values them at that day's close.</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>27.50</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Fees</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Commission or transaction fee; blank defaults to zero.</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Cash rows</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Total cash for DIVIDEND, DEPOSIT, WITHDRAWAL, FEE, and INTEREST rows. Enter it as a positive number; the type decides whether money came in or went out (INTEREST keeps its sign, so margin interest charged can be negative).</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>8.25 or 5000</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Split Ratio</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>SPLIT rows</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>New shares per old share. The cost-basis ledger does not adjust for splits, so a SPLIT row restates that ticker's earlier BUY, SELL, and DRIP rows in post-split shares: shares are multiplied by the ratio and the price divided by it, leaving the cost unchanged. Rows dated before the split are restated, as are rows on the same date listed above the SPLIT row. Dividends are left as they are. A REVERSE SPLIT row accepts the ratio either way round.</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>20:1 or 20 (20-for-1); 1:10 or 0.1 (1-for-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Optional description saved with the transaction.</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Initial purchase</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>BUY, SELL, and DRIP rows update positions when the transaction ledger is the portfolio's source of truth. If current holdings already exist, the import keeps those share counts and adds the transactions for history, cost-basis support, dividend tracking, and realized gains—matching broker transaction imports.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="72" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Account Alpha on the Dashboard: DEPOSIT, WITHDRAWAL, TRANSFER IN, and TRANSFER OUT rows let the app separate money you added or took out from what the account earned. When a file contains any of these rows, the app treats the file's first-to-last date as a complete record of money in and out, so include every deposit and withdrawal for that stretch. A period with no money movements can be marked complete on the Holdings screen under Deposits &amp; Withdrawals.</t>
         </is>
@@ -1137,9 +1176,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A19:D19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
